--- a/data/trending_integrated_20261022_10.xlsx
+++ b/data/trending_integrated_20261022_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7820</v>
+        <v>7910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.42%</t>
+          <t>'+18.77%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>5941854750</v>
+        <v>6197916635</v>
       </c>
       <c r="P2" t="n">
         <v>8430</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 기업 루미아 인수 완료 및 휴머노이드 로봇 관련 기술 개발. 세계 최초 로봇 장갑 센서 개발 성공으로 인한 시총 3조 달성 기대.</t>
+          <t>미국 기업 루미아 인수 관련 루머 및 로봇 관련 신기술 개발 기대감 고조. 휴머노이드 로봇 시장 성장 가능성 언급되며 투자 심리 자극.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['휴머노이드 로봇', '인수', '로봇 장갑']</t>
+          <t>['미국 기업 인수', '로봇 기술', '휴머노이드']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54300</v>
+        <v>3570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.84%</t>
+          <t>'+15.53%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>694</v>
+        <v>225</v>
       </c>
       <c r="H3" t="n">
-        <v>37.72</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>47700</v>
+        <v>3090</v>
       </c>
       <c r="K3" t="n">
-        <v>51000</v>
+        <v>3190</v>
       </c>
       <c r="L3" t="n">
-        <v>56500</v>
+        <v>3600</v>
       </c>
       <c r="M3" t="n">
-        <v>50500</v>
+        <v>3155</v>
       </c>
       <c r="N3" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>366969627100</v>
+        <v>26642064005</v>
       </c>
       <c r="P3" t="n">
-        <v>67300</v>
+        <v>7050</v>
       </c>
       <c r="Q3" t="n">
-        <v>23150</v>
+        <v>2500</v>
       </c>
       <c r="R3" t="n">
-        <v>1440000</v>
+        <v>80000</v>
       </c>
       <c r="S3" t="n">
-        <v>368000</v>
+        <v>9000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>잠정 실적 발표를 통한 어닝 서프라이즈 및 주식 소각 결정, 전망 상향으로 인한 주가 상승 기대감. 5000억 규모 영업이익 달성.</t>
+          <t>북한 지도자 관련 지정학적 리스크 부각되며 관련주로 부각. 전쟁 가능성 및 남북 관계 경색 우려로 인한 주가 급등세.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '실적 전망']</t>
+          <t>['지정학적 리스크', '북한 이슈', '전쟁 가능성']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3455</v>
+        <v>54800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.81%</t>
+          <t>'+14.88%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="G4" t="n">
-        <v>202</v>
+        <v>740</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>37.72</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3090</v>
+        <v>47700</v>
       </c>
       <c r="K4" t="n">
-        <v>3190</v>
+        <v>51000</v>
       </c>
       <c r="L4" t="n">
-        <v>3495</v>
+        <v>56500</v>
       </c>
       <c r="M4" t="n">
-        <v>3155</v>
+        <v>50500</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="O4" t="n">
-        <v>20092023782</v>
+        <v>380767515700</v>
       </c>
       <c r="P4" t="n">
-        <v>7050</v>
+        <v>67300</v>
       </c>
       <c r="Q4" t="n">
-        <v>2500</v>
+        <v>23150</v>
       </c>
       <c r="R4" t="n">
-        <v>80000</v>
+        <v>1440000</v>
       </c>
       <c r="S4" t="n">
-        <v>9000</v>
+        <v>368000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>김정은 신변 이상설 확산에 따른 대북 관련주 급등 가능성. 전쟁 가능성 대두 및 대북 확성기 관련 사업 주목.</t>
+          <t>실적 발표서 역대급 어닝 서프라이즈 기록. 주식 소각 결정 및 전망 상향 공시로 투자 심리 강화. 5천억 영업이익 달성 및 자사주 취득 등으로 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['김정은', '대북 관련주', '전쟁 가능성']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15970</v>
+        <v>1714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.61%</t>
+          <t>'+6.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14980</v>
+        <v>1610</v>
       </c>
       <c r="K5" t="n">
-        <v>14460</v>
+        <v>1655</v>
       </c>
       <c r="L5" t="n">
-        <v>16140</v>
+        <v>1780</v>
       </c>
       <c r="M5" t="n">
-        <v>13550</v>
+        <v>1622</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>42945479910</v>
+        <v>7259013057</v>
       </c>
       <c r="P5" t="n">
-        <v>28800</v>
+        <v>3980</v>
       </c>
       <c r="Q5" t="n">
-        <v>12030</v>
+        <v>1115</v>
       </c>
       <c r="R5" t="n">
-        <v>-47000</v>
+        <v>100000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>조선일보 및 대만 반도체 파업 관련 뉴스가 언급되었으며, 신규 상장주로 수급이 쏠릴 가능성과 주가 하락에 대한 언급이 존재.</t>
+          <t>연이은 하한가 기록 및 주가 조작 의혹 제기. 매각 관련 불확실성 및 정보 부족으로 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '신규상장주', '보호예수']</t>
+          <t>['주가 조작', '매각 불확실성', '하한가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1690</v>
+        <v>19050</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.97%</t>
+          <t>'+6.31%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.39</v>
+        <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>3.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1610</v>
+        <v>17920</v>
       </c>
       <c r="K6" t="n">
-        <v>1655</v>
+        <v>19180</v>
       </c>
       <c r="L6" t="n">
-        <v>1780</v>
+        <v>20150</v>
       </c>
       <c r="M6" t="n">
-        <v>1622</v>
+        <v>18860</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>6409800353</v>
+        <v>53195795360</v>
       </c>
       <c r="P6" t="n">
-        <v>3980</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>1115</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>100000</v>
+        <v>-7000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>이전 하한가 두 방에 대한 원인 불명확 및 주가 조작 의혹 제기. 매각 가능성에 대한 기대와 우려 공존.</t>
+          <t>미국 보안 이슈 확산 및 PHP 웹사이트 보안 취약점 발견에 따른 보안주 급등 기대. AI 발전으로 인한 보안 분야 성장 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 조작', '하한가', '매각']</t>
+          <t>['보안', 'PHP', 'AI']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14530</v>
+        <v>14550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.54%</t>
+          <t>'+1.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.33</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="H7" t="n">
         <v>3.48</v>
@@ -1070,7 +1070,7 @@
         <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>59529705180</v>
+        <v>62930040920</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>엔비디아 AI 광통신 관련 기술 확보 및 EUV용 유리기판 제조 기술 인정. AI 광통신 열풍에 따른 수혜 기대감.</t>
+          <t>AI 광통신 관련 뉴스 및 EUV용 유리기판 제조 기술 확보 소식에 따른 기대감 고조. 기관 매집 움직임 포착되며 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI 광통신', 'EUV', '유리기판']</t>
+          <t>['AI 광통신', 'EUV 유리기판', '기관 매집']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14970</v>
+        <v>14940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.35%</t>
+          <t>'+1.15%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H8" t="n">
         <v>9.949999999999999</v>
@@ -1162,7 +1162,7 @@
         <v>9.82</v>
       </c>
       <c r="O8" t="n">
-        <v>21519769755</v>
+        <v>22785133975</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>221000</v>
+        <v>15130</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.12%</t>
+          <t>'+1.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>466</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>2678</v>
+        <v>57</v>
       </c>
       <c r="H9" t="n">
-        <v>46.14</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>223500</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>221500</v>
+        <v>14460</v>
       </c>
       <c r="L9" t="n">
-        <v>226000</v>
+        <v>16140</v>
       </c>
       <c r="M9" t="n">
-        <v>220000</v>
+        <v>13550</v>
       </c>
       <c r="N9" t="n">
-        <v>46.08</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>686437657250</v>
+        <v>56351878860</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>28800</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>12030</v>
       </c>
       <c r="R9" t="n">
-        <v>-89000</v>
+        <v>-47000</v>
       </c>
       <c r="S9" t="n">
-        <v>-156000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>메타 호실적 및 AI 투자 확대 소식에 따른 기대감. 반도체 업황 개선 및 온디바이스 AI 관련 수요 증가 전망. 외국인 투자자 움직임 주목.</t>
+          <t>조선일보 및 대만 반도체 파업 이슈와 함께 신규 상장주로 수급 분산 우려. 외인 매도세 및 보호예수 해제 물량 부담.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 투자', '반도체', '메모리 수요']</t>
+          <t>['보호예수', '수급', '매도세']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7240</v>
+        <v>220750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-1.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>466</v>
       </c>
       <c r="G10" t="n">
-        <v>137</v>
+        <v>2443</v>
       </c>
       <c r="H10" t="n">
-        <v>25.47</v>
+        <v>46.14</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7350</v>
+        <v>223500</v>
       </c>
       <c r="K10" t="n">
-        <v>7270</v>
+        <v>221500</v>
       </c>
       <c r="L10" t="n">
-        <v>7340</v>
+        <v>226000</v>
       </c>
       <c r="M10" t="n">
-        <v>7210</v>
+        <v>220000</v>
       </c>
       <c r="N10" t="n">
-        <v>25.45</v>
+        <v>46.08</v>
       </c>
       <c r="O10" t="n">
-        <v>4475396810</v>
+        <v>731024348500</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>7190</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-47000</v>
+        <v>-89000</v>
       </c>
       <c r="S10" t="n">
-        <v>-18000</v>
+        <v>-156000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 하락 우려 속에서 바닥권 매수 기회 언급. OLED 기술 경쟁 및 TV 사업 전망.</t>
+          <t>반도체 업황 개선 기대 속에서도 국내 증시의 외국인 수급 불안정 및 변동성 확대. 김정은 관련 뉴스 등 외부 요인에 따른 시장 불안감 고조.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적 발표', 'OLED', '바닥권']</t>
+          <t>['반도체', '외국인 수급', '변동성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1274000</v>
+        <v>1275000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.55%</t>
+          <t>'-1.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G11" t="n">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="H11" t="n">
         <v>48.79</v>
@@ -1438,7 +1438,7 @@
         <v>48.77</v>
       </c>
       <c r="O11" t="n">
-        <v>868121647500</v>
+        <v>911799148500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>최태원 회장 관련 논란 및 주가 하락 우려. 외국인 매도세 증가 및 솔리다임 상장 계획 관련 불확실성.</t>
+          <t>경영진 관련 부정적 언급 및 시장 불안감 고조. 외국인 매도 증가 및 국내 증시 전반의 약세 흐름 속에서 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['최태원', '외국인 매도', '솔리다임']</t>
+          <t>['경영진 리스크', '외국인 매도', '시장 불안']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41400</v>
+        <v>7240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.24%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>460</v>
+        <v>184</v>
       </c>
       <c r="H12" t="n">
-        <v>13.09</v>
+        <v>25.47</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>42350</v>
+        <v>7350</v>
       </c>
       <c r="K12" t="n">
-        <v>41850</v>
+        <v>7270</v>
       </c>
       <c r="L12" t="n">
-        <v>42350</v>
+        <v>7340</v>
       </c>
       <c r="M12" t="n">
-        <v>41150</v>
+        <v>7210</v>
       </c>
       <c r="N12" t="n">
-        <v>13.23</v>
+        <v>25.45</v>
       </c>
       <c r="O12" t="n">
-        <v>5374873775</v>
+        <v>4663424920</v>
       </c>
       <c r="P12" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>24150</v>
+        <v>7190</v>
       </c>
       <c r="R12" t="n">
-        <v>11000</v>
+        <v>-47000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>간암 치료제 승인에 대한 기대감과 함께, FDA 승인 요건 미충족 가능성 및 공매도 세력에 대한 경계가 공존하는 상황.</t>
+          <t>실적 발표 후 주가 급락 및 투자자들의 불만 고조. OLED 사업 관련 불확실성 및 적자 지속으로 인한 투자 심리 악화.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['간암치료제', 'FDA승인', '공매도']</t>
+          <t>['실적 발표', 'OLED', '적자']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9890</v>
+        <v>41550</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-1.89%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.53</v>
+        <v>-0.14</v>
       </c>
       <c r="E13" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>261</v>
+        <v>492</v>
       </c>
       <c r="H13" t="n">
-        <v>5.87</v>
+        <v>13.09</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10190</v>
+        <v>42350</v>
       </c>
       <c r="K13" t="n">
-        <v>10110</v>
+        <v>41850</v>
       </c>
       <c r="L13" t="n">
-        <v>10180</v>
+        <v>42350</v>
       </c>
       <c r="M13" t="n">
-        <v>9720</v>
+        <v>41150</v>
       </c>
       <c r="N13" t="n">
-        <v>5.34</v>
+        <v>13.23</v>
       </c>
       <c r="O13" t="n">
-        <v>8647317470</v>
+        <v>5614137500</v>
       </c>
       <c r="P13" t="n">
-        <v>14940</v>
+        <v>69200</v>
       </c>
       <c r="Q13" t="n">
-        <v>5390</v>
+        <v>24150</v>
       </c>
       <c r="R13" t="n">
-        <v>-84000</v>
+        <v>11000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>테슬라 실적 호조 및 스페이스X 상장 이슈에 따른 기대감. 그러나 대규모 공매도 물량 및 개인 투자자 매물 출회.</t>
+          <t>간암 치료제 FDA 승인 기대감 속에서 기관 매수세 유입. 공매도 세력과의 공방 및 승인 여부에 대한 불확실성 지속.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['테슬라', '공매도', '스페이스X']</t>
+          <t>['FDA 승인', '공매도', '기관 매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,97 +1660,189 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10340</v>
+        <v>9970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-7.18%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.41</v>
+        <v>0.53</v>
       </c>
       <c r="E14" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H14" t="n">
-        <v>3.69</v>
+        <v>5.87</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>11140</v>
+        <v>10190</v>
       </c>
       <c r="K14" t="n">
-        <v>10830</v>
+        <v>10110</v>
       </c>
       <c r="L14" t="n">
-        <v>10880</v>
+        <v>10180</v>
       </c>
       <c r="M14" t="n">
-        <v>10050</v>
+        <v>9720</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>5.34</v>
       </c>
       <c r="O14" t="n">
-        <v>37063514040</v>
+        <v>9114658100</v>
       </c>
       <c r="P14" t="n">
-        <v>11690</v>
+        <v>14940</v>
       </c>
       <c r="Q14" t="n">
-        <v>2270</v>
+        <v>5390</v>
       </c>
       <c r="R14" t="n">
-        <v>-188000</v>
+        <v>-84000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>로봇주 급등 시장에 대한 언급과 투자 경고, 급락 가능성 및 개인 투자자들의 혼란이 혼재된 상황.</t>
+          <t>테슬라 실적 발표 및 관련 이슈에 따른 변동성 확대. 투자자들의 엇갈리는 심리가 차트 상에서 나타나며 공매도 우려 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['투자경고', '급락', '개인투자자']</t>
+          <t>['테슬라', '실적 발표', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10250</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-7.99%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E15" t="n">
+        <v>104</v>
+      </c>
+      <c r="F15" t="n">
+        <v>63</v>
+      </c>
+      <c r="G15" t="n">
+        <v>289</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>11140</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10830</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10880</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10050</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O15" t="n">
+        <v>38697575020</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-188000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>로봇주 테마의 변동성 확대 및 투자 경고 종목 지정. ESS 마진율 불확실성 등 실질적인 성장 동력에 대한 의문 제기.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['로봇 테마', '투자 경고', 'ESS 마진율']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>5</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>396300</t>
         </is>

--- a/data/trending_integrated_20261022_10.xlsx
+++ b/data/trending_integrated_20261022_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7910</v>
+        <v>7740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.77%</t>
+          <t>'+16.22%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6197916635</v>
+        <v>6518017435</v>
       </c>
       <c r="P2" t="n">
         <v>8430</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 기업 루미아 인수 관련 루머 및 로봇 관련 신기술 개발 기대감 고조. 휴머노이드 로봇 시장 성장 가능성 언급되며 투자 심리 자극.</t>
+          <t>미국 기업 루미아 인수 및 로봇 장갑 개발 등 강력한 신규 사업 모멘텀에 대한 기대감이 반영됨. 외인 매수세 유입과 함께 시총 3조원 달성 가능성이 언급되는 등 긍정적 전망이 우세함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['미국 기업 인수', '로봇 기술', '휴머노이드']</t>
+          <t>['루미아', '인수', '로봇']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3570</v>
+        <v>3585</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.53%</t>
+          <t>'+16.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>3190</v>
       </c>
       <c r="L3" t="n">
-        <v>3600</v>
+        <v>3615</v>
       </c>
       <c r="M3" t="n">
         <v>3155</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>26642064005</v>
+        <v>30332706057</v>
       </c>
       <c r="P3" t="n">
         <v>7050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>북한 지도자 관련 지정학적 리스크 부각되며 관련주로 부각. 전쟁 가능성 및 남북 관계 경색 우려로 인한 주가 급등세.</t>
+          <t>김정은 위원장 신변 이상설 및 북한 관련 지정학적 리스크가 부각되며 급등 가능성이 대두됨. 전쟁 가능성 및 빅텍의 과거 급등 이력 언급과 함께 기관 투신 매수세 유입이 긍정적으로 해석됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '북한 이슈', '전쟁 가능성']</t>
+          <t>['지정학적 리스크', '김정은', '기관']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54800</v>
+        <v>55000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.88%</t>
+          <t>'+15.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F4" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G4" t="n">
-        <v>740</v>
+        <v>768</v>
       </c>
       <c r="H4" t="n">
         <v>37.72</v>
@@ -794,7 +794,7 @@
         <v>37.7</v>
       </c>
       <c r="O4" t="n">
-        <v>380767515700</v>
+        <v>392088312800</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1714</v>
+        <v>1726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.46%</t>
+          <t>'+7.20%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>7259013057</v>
+        <v>8036248551</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>연이은 하한가 기록 및 주가 조작 의혹 제기. 매각 관련 불확실성 및 정보 부족으로 투자 심리 위축.</t>
+          <t>과거 하한가 두 번에 대한 원인 분석과 함께, 매각 관련 불확실성 및 주가 조작 의혹이 제기됨. 호재 여부에 대한 논란과 함께 단기 트레이딩 관점이 일부 나타남.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가 조작', '매각 불확실성', '하한가']</t>
+          <t>['매각', '주가 조작', '하한가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19050</v>
+        <v>18560</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.31%</t>
+          <t>'+3.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H6" t="n">
         <v>3.29</v>
@@ -972,13 +972,13 @@
         <v>20150</v>
       </c>
       <c r="M6" t="n">
-        <v>18860</v>
+        <v>18430</v>
       </c>
       <c r="N6" t="n">
         <v>3.61</v>
       </c>
       <c r="O6" t="n">
-        <v>53195795360</v>
+        <v>56088654030</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 보안 이슈 확산 및 PHP 웹사이트 보안 취약점 발견에 따른 보안주 급등 기대. AI 발전으로 인한 보안 분야 성장 전망.</t>
+          <t>미국 보안주 급등 및 PHP 해킹 비상 뉴스로 인한 보안 이슈 부각. 라온시큐어를 보안 대장으로 지목하며 기대감 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안', 'PHP', 'AI']</t>
+          <t>['보안주', 'PHP', '해킹']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14550</v>
+        <v>14880</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>284</v>
+        <v>148</v>
       </c>
       <c r="H7" t="n">
-        <v>3.48</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14310</v>
+        <v>14770</v>
       </c>
       <c r="K7" t="n">
-        <v>14180</v>
+        <v>14770</v>
       </c>
       <c r="L7" t="n">
-        <v>14830</v>
+        <v>15290</v>
       </c>
       <c r="M7" t="n">
-        <v>13890</v>
+        <v>14770</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>62930040920</v>
+        <v>24290509355</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>1640</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-368000</v>
+        <v>-95000</v>
       </c>
       <c r="S7" t="n">
-        <v>9000</v>
+        <v>-14000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 광통신 관련 뉴스 및 EUV용 유리기판 제조 기술 확보 소식에 따른 기대감 고조. 기관 매집 움직임 포착되며 주가 상승 전망.</t>
+          <t>외국인 및 연기금의 지속적인 매수를 기반으로 한 실적 우량주로서의 대우건설에 대한 긍정적 언급이 나타남. 다만, 정치 관련 부정적 내용과 함께 건설주 전반의 상승 기대도 일부 존재함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI 광통신', 'EUV 유리기판', '기관 매집']</t>
+          <t>['외국인', '연기금', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14940</v>
+        <v>14370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.15%</t>
+          <t>'+0.42%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>139</v>
+        <v>293</v>
       </c>
       <c r="H8" t="n">
-        <v>9.949999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14770</v>
+        <v>14310</v>
       </c>
       <c r="K8" t="n">
-        <v>14770</v>
+        <v>14180</v>
       </c>
       <c r="L8" t="n">
-        <v>15290</v>
+        <v>14830</v>
       </c>
       <c r="M8" t="n">
-        <v>14770</v>
+        <v>13890</v>
       </c>
       <c r="N8" t="n">
-        <v>9.82</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>22785133975</v>
+        <v>67636135340</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R8" t="n">
-        <v>-95000</v>
+        <v>-368000</v>
       </c>
       <c r="S8" t="n">
-        <v>-14000</v>
+        <v>9000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외국인 및 연기금의 지속적인 매수세와 실적 우량주로서의 가능성 언급. 건설주 전반의 상승 기대감.</t>
+          <t>엔비디아 AI 광통신 관련 뉴스 및 EUV용 유리기판 제조 기술 확보 등 구체적인 기술적 호재가 연이어 발생하며 급등 기대감이 고조됨. 기관 매집 시작 및 15000원 돌파 전망이 제시됨.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['건설주', '외국인 매수', '실적 우량주']</t>
+          <t>['AI', '광통신', 'EUV']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15130</v>
+        <v>14900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.00%</t>
+          <t>'-0.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1.2</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="H9" t="n">
         <v>1.2</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>56351878860</v>
+        <v>61393690810</v>
       </c>
       <c r="P9" t="n">
         <v>28800</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>조선일보 및 대만 반도체 파업 이슈와 함께 신규 상장주로 수급 분산 우려. 외인 매도세 및 보호예수 해제 물량 부담.</t>
+          <t>대만 반도체 파업 및 신규 상장주로의 수급 쏠림 우려 속에서 하락세를 보임. 외인 매도세 및 보호예수 해제 물량 부담감이 작용하며, 전반적으로 부정적인 의견이 지배적임.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보호예수', '수급', '매도세']</t>
+          <t>['반도체', '외인', '보호예수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>220750</v>
+        <v>220250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.23%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="G10" t="n">
-        <v>2443</v>
+        <v>2008</v>
       </c>
       <c r="H10" t="n">
         <v>46.14</v>
@@ -1340,13 +1340,13 @@
         <v>226000</v>
       </c>
       <c r="M10" t="n">
-        <v>220000</v>
+        <v>219500</v>
       </c>
       <c r="N10" t="n">
         <v>46.08</v>
       </c>
       <c r="O10" t="n">
-        <v>731024348500</v>
+        <v>780262732750</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 기대 속에서도 국내 증시의 외국인 수급 불안정 및 변동성 확대. 김정은 관련 뉴스 등 외부 요인에 따른 시장 불안감 고조.</t>
+          <t>외국인 매매 패턴에 대한 불만과 함께 반도체 섹터의 슈퍼마이크로 급등에 따른 삼성전자 급등 전망이 일부 혼재되어 나타남. 전반적으로 국내 증시 및 정치 관련 부정적 언급이 많음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '외국인 수급', '변동성']</t>
+          <t>['외국인', '반도체', '전망']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1275000</v>
+        <v>7240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.47%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>497</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>1813</v>
+        <v>198</v>
       </c>
       <c r="H11" t="n">
-        <v>48.79</v>
+        <v>25.47</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1294000</v>
+        <v>7350</v>
       </c>
       <c r="K11" t="n">
-        <v>1273000</v>
+        <v>7270</v>
       </c>
       <c r="L11" t="n">
-        <v>1297000</v>
+        <v>7340</v>
       </c>
       <c r="M11" t="n">
-        <v>1267000</v>
+        <v>7210</v>
       </c>
       <c r="N11" t="n">
-        <v>48.77</v>
+        <v>25.45</v>
       </c>
       <c r="O11" t="n">
-        <v>911799148500</v>
+        <v>5000629240</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>468000</v>
+        <v>7190</v>
       </c>
       <c r="R11" t="n">
-        <v>-36000</v>
+        <v>-47000</v>
       </c>
       <c r="S11" t="n">
-        <v>10000</v>
+        <v>-18000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>경영진 관련 부정적 언급 및 시장 불안감 고조. 외국인 매도 증가 및 국내 증시 전반의 약세 흐름 속에서 주가 하락 우려.</t>
+          <t>실적 발표 및 OLED 관련 이슈 속에서 LG 그룹주 전반에 대한 부정적 인식이 존재함. 적자 지속 및 저 PBR 수준에도 불구하고 기대감은 낮으며, '10원짜리 주식'이라는 비판적 언급이 나타남.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['경영진 리스크', '외국인 매도', '시장 불안']</t>
+          <t>['실적', 'OLED', 'PBR']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7240</v>
+        <v>41500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>184</v>
+        <v>524</v>
       </c>
       <c r="H12" t="n">
-        <v>25.47</v>
+        <v>13.09</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7350</v>
+        <v>42350</v>
       </c>
       <c r="K12" t="n">
-        <v>7270</v>
+        <v>41850</v>
       </c>
       <c r="L12" t="n">
-        <v>7340</v>
+        <v>42350</v>
       </c>
       <c r="M12" t="n">
-        <v>7210</v>
+        <v>41150</v>
       </c>
       <c r="N12" t="n">
-        <v>25.45</v>
+        <v>13.23</v>
       </c>
       <c r="O12" t="n">
-        <v>4663424920</v>
+        <v>5873190050</v>
       </c>
       <c r="P12" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q12" t="n">
-        <v>7190</v>
+        <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>-47000</v>
+        <v>11000</v>
       </c>
       <c r="S12" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 급락 및 투자자들의 불만 고조. OLED 사업 관련 불확실성 및 적자 지속으로 인한 투자 심리 악화.</t>
+          <t>간암 승인 기대감 속 기관 매수세 확인. 공매도 세력 경고 및 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적 발표', 'OLED', '적자']</t>
+          <t>['간암 승인', '기관 매수', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41550</v>
+        <v>1267000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.89%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>113</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>68</v>
+        <v>497</v>
       </c>
       <c r="G13" t="n">
-        <v>492</v>
+        <v>1829</v>
       </c>
       <c r="H13" t="n">
-        <v>13.09</v>
+        <v>48.79</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>42350</v>
+        <v>1294000</v>
       </c>
       <c r="K13" t="n">
-        <v>41850</v>
+        <v>1273000</v>
       </c>
       <c r="L13" t="n">
-        <v>42350</v>
+        <v>1297000</v>
       </c>
       <c r="M13" t="n">
-        <v>41150</v>
+        <v>1266000</v>
       </c>
       <c r="N13" t="n">
-        <v>13.23</v>
+        <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>5614137500</v>
+        <v>954547197000</v>
       </c>
       <c r="P13" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>24150</v>
+        <v>468000</v>
       </c>
       <c r="R13" t="n">
-        <v>11000</v>
+        <v>-36000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>간암 치료제 FDA 승인 기대감 속에서 기관 매수세 유입. 공매도 세력과의 공방 및 승인 여부에 대한 불확실성 지속.</t>
+          <t>국내 증시 및 정치 상황에 대한 강한 불만과 함께, 솔리다임 상장 철회 가능성 및 외국인 매도 증가에 대한 우려가 나타남. 전반적으로 부정적인 분위기가 지배적임.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '기관 매수']</t>
+          <t>['정치', '외국인', '솔리다임']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9970</v>
+        <v>9930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.16%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H14" t="n">
         <v>5.87</v>
@@ -1714,7 +1714,7 @@
         <v>5.34</v>
       </c>
       <c r="O14" t="n">
-        <v>9114658100</v>
+        <v>9527562390</v>
       </c>
       <c r="P14" t="n">
         <v>14940</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>테슬라 실적 발표 및 관련 이슈에 따른 변동성 확대. 투자자들의 엇갈리는 심리가 차트 상에서 나타나며 공매도 우려 제기.</t>
+          <t>테슬라 실적 상회 및 스페이스X 상장 이슈 등 잠재적 호재와 함께, 공매도 및 개인 물량 털기에 대한 우려가 혼재된 양상. 분봉 차트 분석 및 개미 털기 언급이 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테슬라', '실적 발표', '공매도']</t>
+          <t>['테슬라', '공매도', '차트']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>38697575020</v>
+        <v>39956728735</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 테마의 변동성 확대 및 투자 경고 종목 지정. ESS 마진율 불확실성 등 실질적인 성장 동력에 대한 의문 제기.</t>
+          <t>로봇주 급등 관련 기대감 속 투기 과열 종목 지정 및 ESS 마진율 불확실성 언급. 급락 및 반등 불가 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇 테마', '투자 경고', 'ESS 마진율']</t>
+          <t>['로봇주', '투기과열', 'ESS']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_10.xlsx
+++ b/data/trending_integrated_20261022_10.xlsx
@@ -563,70 +563,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>유니켐</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7740</v>
+        <v>3622</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.22%</t>
+          <t>'+17.22%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>71</v>
+        <v>307</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6660</v>
+        <v>3090</v>
       </c>
       <c r="K2" t="n">
-        <v>6710</v>
+        <v>3190</v>
       </c>
       <c r="L2" t="n">
-        <v>8430</v>
+        <v>3700</v>
       </c>
       <c r="M2" t="n">
-        <v>6640</v>
+        <v>3155</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6518017435</v>
+        <v>35714460534</v>
       </c>
       <c r="P2" t="n">
-        <v>8430</v>
+        <v>7050</v>
       </c>
       <c r="Q2" t="n">
-        <v>391</v>
+        <v>2500</v>
       </c>
       <c r="R2" t="n">
-        <v>14000</v>
+        <v>80000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 기업 루미아 인수 및 로봇 장갑 개발 등 강력한 신규 사업 모멘텀에 대한 기대감이 반영됨. 외인 매수세 유입과 함께 시총 3조원 달성 가능성이 언급되는 등 긍정적 전망이 우세함.</t>
+          <t>북한 김정은 위원장 관련 신변 이상설 및 사망설에 따른 급등세. 전쟁 가능성 대두 및 관련주로서의 움직임 집중.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['루미아', '인수', '로봇']</t>
+          <t>['김정은', '신변 이상설', '전쟁']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>011330</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3585</v>
+        <v>55800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.02%</t>
+          <t>'+16.98%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="G3" t="n">
-        <v>265</v>
+        <v>782</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>37.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3090</v>
+        <v>47700</v>
       </c>
       <c r="K3" t="n">
-        <v>3190</v>
+        <v>51000</v>
       </c>
       <c r="L3" t="n">
-        <v>3615</v>
+        <v>56500</v>
       </c>
       <c r="M3" t="n">
-        <v>3155</v>
+        <v>50500</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>30332706057</v>
+        <v>411986879450</v>
       </c>
       <c r="P3" t="n">
-        <v>7050</v>
+        <v>67300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2500</v>
+        <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>80000</v>
+        <v>1440000</v>
       </c>
       <c r="S3" t="n">
-        <v>9000</v>
+        <v>368000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>김정은 위원장 신변 이상설 및 북한 관련 지정학적 리스크가 부각되며 급등 가능성이 대두됨. 전쟁 가능성 및 빅텍의 과거 급등 이력 언급과 함께 기관 투신 매수세 유입이 긍정적으로 해석됨.</t>
+          <t>실적 발표서 역대급 어닝 서프라이즈 기록. 주식 소각 결정 및 전망 상향 공시로 투자 심리 강화. 5천억 영업이익 달성 및 자사주 취득 등으로 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '김정은', '기관']</t>
+          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>유니켐</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55000</v>
+        <v>7790</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.30%</t>
+          <t>'+16.97%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>768</v>
+        <v>82</v>
       </c>
       <c r="H4" t="n">
-        <v>37.72</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>47700</v>
+        <v>6660</v>
       </c>
       <c r="K4" t="n">
-        <v>51000</v>
+        <v>6710</v>
       </c>
       <c r="L4" t="n">
-        <v>56500</v>
+        <v>8430</v>
       </c>
       <c r="M4" t="n">
-        <v>50500</v>
+        <v>6640</v>
       </c>
       <c r="N4" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>392088312800</v>
+        <v>6636540260</v>
       </c>
       <c r="P4" t="n">
-        <v>67300</v>
+        <v>8430</v>
       </c>
       <c r="Q4" t="n">
-        <v>23150</v>
+        <v>391</v>
       </c>
       <c r="R4" t="n">
-        <v>1440000</v>
+        <v>14000</v>
       </c>
       <c r="S4" t="n">
-        <v>368000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>실적 발표서 역대급 어닝 서프라이즈 기록. 주식 소각 결정 및 전망 상향 공시로 투자 심리 강화. 5천억 영업이익 달성 및 자사주 취득 등으로 주가 상승 기대.</t>
+          <t>미국 기업 루미아 인수 기반 휴머노이드 로봇 사업 관련 호재 집중. 해외 기업 인수 및 기술 개발 성공 시 높은 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
+          <t>['루미아', '인수', '휴머노이드']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>011330</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1726</v>
+        <v>18590</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.20%</t>
+          <t>'+3.74%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.39</v>
+        <v>-0.32</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>3.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1610</v>
+        <v>17920</v>
       </c>
       <c r="K5" t="n">
-        <v>1655</v>
+        <v>19180</v>
       </c>
       <c r="L5" t="n">
-        <v>1780</v>
+        <v>20150</v>
       </c>
       <c r="M5" t="n">
-        <v>1622</v>
+        <v>18370</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="O5" t="n">
-        <v>8036248551</v>
+        <v>58051916050</v>
       </c>
       <c r="P5" t="n">
-        <v>3980</v>
+        <v>22450</v>
       </c>
       <c r="Q5" t="n">
-        <v>1115</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>100000</v>
+        <v>-7000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>과거 하한가 두 번에 대한 원인 분석과 함께, 매각 관련 불확실성 및 주가 조작 의혹이 제기됨. 호재 여부에 대한 논란과 함께 단기 트레이딩 관점이 일부 나타남.</t>
+          <t>PHP 해킹 이슈로 인한 보안주 급등 기대감 형성. 하지만 단기 급등 후 개인 매물 출회 및 외국인 단타 흐름 관측.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['매각', '주가 조작', '하한가']</t>
+          <t>['보안 이슈', 'PHP 해킹', '단기 급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18560</v>
+        <v>1667</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.57%</t>
+          <t>'+3.54%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.32</v>
+        <v>-0.39</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="H6" t="n">
-        <v>3.29</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17920</v>
+        <v>1610</v>
       </c>
       <c r="K6" t="n">
-        <v>19180</v>
+        <v>1655</v>
       </c>
       <c r="L6" t="n">
-        <v>20150</v>
+        <v>1780</v>
       </c>
       <c r="M6" t="n">
-        <v>18430</v>
+        <v>1622</v>
       </c>
       <c r="N6" t="n">
-        <v>3.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>56088654030</v>
+        <v>8609323682</v>
       </c>
       <c r="P6" t="n">
-        <v>22450</v>
+        <v>3980</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>1115</v>
       </c>
       <c r="R6" t="n">
-        <v>-7000</v>
+        <v>100000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 보안주 급등 및 PHP 해킹 비상 뉴스로 인한 보안 이슈 부각. 라온시큐어를 보안 대장으로 지목하며 기대감 형성.</t>
+          <t>매각 관련 불확실성과 주가 급락 경험 후 반등 기대감. 주가 조작 의혹 및 공시 내용에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', 'PHP', '해킹']</t>
+          <t>['매각', '주가 조작', '호재']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14880</v>
+        <v>14970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.74%</t>
+          <t>'+1.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
         <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>24290509355</v>
+        <v>25248628630</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외국인 및 연기금의 지속적인 매수를 기반으로 한 실적 우량주로서의 대우건설에 대한 긍정적 언급이 나타남. 다만, 정치 관련 부정적 내용과 함께 건설주 전반의 상승 기대도 일부 존재함.</t>
+          <t>외국인 및 연기금 매수세 유입에 대한 기대감과 실적 우량주로서의 가능성 언급. 정치적 메시지와 주가 조작 의혹 관련 내용 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14370</v>
+        <v>15110</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.42%</t>
+          <t>'+0.87%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.33</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="H8" t="n">
-        <v>3.48</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14310</v>
+        <v>14980</v>
       </c>
       <c r="K8" t="n">
-        <v>14180</v>
+        <v>14460</v>
       </c>
       <c r="L8" t="n">
-        <v>14830</v>
+        <v>16140</v>
       </c>
       <c r="M8" t="n">
-        <v>13890</v>
+        <v>13550</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>67636135340</v>
+        <v>63827544785</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>28800</v>
       </c>
       <c r="Q8" t="n">
-        <v>1640</v>
+        <v>12030</v>
       </c>
       <c r="R8" t="n">
-        <v>-368000</v>
+        <v>-47000</v>
       </c>
       <c r="S8" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>엔비디아 AI 광통신 관련 뉴스 및 EUV용 유리기판 제조 기술 확보 등 구체적인 기술적 호재가 연이어 발생하며 급등 기대감이 고조됨. 기관 매집 시작 및 15000원 돌파 전망이 제시됨.</t>
+          <t>반도체 섹터 전반의 흐름 및 대만 반도체 파업 관련 소식에 따른 변동성. 신규 상장주 수급 이동 및 AI, 반도체 관련 기대감 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '광통신', 'EUV']</t>
+          <t>['반도체', 'AI', '수급']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14900</v>
+        <v>14360</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.53%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>0.33</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>69</v>
+        <v>308</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2</v>
+        <v>3.48</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>14310</v>
       </c>
       <c r="K9" t="n">
-        <v>14460</v>
+        <v>14180</v>
       </c>
       <c r="L9" t="n">
-        <v>16140</v>
+        <v>14830</v>
       </c>
       <c r="M9" t="n">
-        <v>13550</v>
+        <v>13890</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>61393690810</v>
+        <v>70163270950</v>
       </c>
       <c r="P9" t="n">
-        <v>28800</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>12030</v>
+        <v>1640</v>
       </c>
       <c r="R9" t="n">
-        <v>-47000</v>
+        <v>-368000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대만 반도체 파업 및 신규 상장주로의 수급 쏠림 우려 속에서 하락세를 보임. 외인 매도세 및 보호예수 해제 물량 부담감이 작용하며, 전반적으로 부정적인 의견이 지배적임.</t>
+          <t>엔비디아 AI 광통신 관련 뉴스 및 EUV용 유리기판 제조 기술 확보 등 구체적인 기술적 호재가 연이어 발생하며 급등 기대감이 고조됨. 기관 매집 시작 및 15000원 돌파 전망이 제시됨.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.05</v>
+        <v>0.55</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '외인', '보호예수']</t>
+          <t>['AI', '광통신', 'EUV']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>220250</v>
+        <v>220750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-1.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G10" t="n">
-        <v>2008</v>
+        <v>1862</v>
       </c>
       <c r="H10" t="n">
         <v>46.14</v>
@@ -1346,7 +1346,7 @@
         <v>46.08</v>
       </c>
       <c r="O10" t="n">
-        <v>780262732750</v>
+        <v>803980517500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외국인 매매 패턴에 대한 불만과 함께 반도체 섹터의 슈퍼마이크로 급등에 따른 삼성전자 급등 전망이 일부 혼재되어 나타남. 전반적으로 국내 증시 및 정치 관련 부정적 언급이 많음.</t>
+          <t>외국인 거래 패턴에 대한 불만과 함께 반도체 섹터 전반의 흐름에 따른 하락세 지속 전망. 일부 긍정적 전망도 있으나 객관적 근거 부족.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외국인', '반도체', '전망']</t>
+          <t>['외국인', '반도체', '수급']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
         <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="H11" t="n">
         <v>25.47</v>
@@ -1438,7 +1438,7 @@
         <v>25.45</v>
       </c>
       <c r="O11" t="n">
-        <v>5000629240</v>
+        <v>5249091955</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>실적 발표 및 OLED 관련 이슈 속에서 LG 그룹주 전반에 대한 부정적 인식이 존재함. 적자 지속 및 저 PBR 수준에도 불구하고 기대감은 낮으며, '10원짜리 주식'이라는 비판적 언급이 나타남.</t>
+          <t>지속적인 적자와 낮은 주가 수준에 대한 불만. 실적 부진에도 불구하고 바닥권이라는 인식과 함께 단기 반등 가능성 언급. OLED 관련 뉴스 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', 'OLED', 'PBR']</t>
+          <t>['실적 부진', '바닥권', 'OLED']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41500</v>
+        <v>1272000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>120</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
+        <v>503</v>
       </c>
       <c r="G12" t="n">
-        <v>524</v>
+        <v>1789</v>
       </c>
       <c r="H12" t="n">
-        <v>13.09</v>
+        <v>48.79</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>42350</v>
+        <v>1294000</v>
       </c>
       <c r="K12" t="n">
-        <v>41850</v>
+        <v>1273000</v>
       </c>
       <c r="L12" t="n">
-        <v>42350</v>
+        <v>1297000</v>
       </c>
       <c r="M12" t="n">
-        <v>41150</v>
+        <v>1266000</v>
       </c>
       <c r="N12" t="n">
-        <v>13.23</v>
+        <v>48.77</v>
       </c>
       <c r="O12" t="n">
-        <v>5873190050</v>
+        <v>990274500500</v>
       </c>
       <c r="P12" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>24150</v>
+        <v>468000</v>
       </c>
       <c r="R12" t="n">
-        <v>11000</v>
+        <v>-36000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>간암 승인 기대감 속 기관 매수세 확인. 공매도 세력 경고 및 긍정적 전망 언급.</t>
+          <t>정치적 리스크 및 경영진 관련 부정적 언급과 함께 외국인 매도세 증가, 주가 하락에 대한 불만 표출. 일부 긍정적 수급 변화 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['간암 승인', '기관 매수', '공매도']</t>
+          <t>['정치적 리스크', '외국인', '주가 하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1267000</v>
+        <v>41500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>128</v>
       </c>
       <c r="F13" t="n">
-        <v>497</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>1829</v>
+        <v>550</v>
       </c>
       <c r="H13" t="n">
-        <v>48.79</v>
+        <v>13.09</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1294000</v>
+        <v>42350</v>
       </c>
       <c r="K13" t="n">
-        <v>1273000</v>
+        <v>41850</v>
       </c>
       <c r="L13" t="n">
-        <v>1297000</v>
+        <v>42350</v>
       </c>
       <c r="M13" t="n">
-        <v>1266000</v>
+        <v>41150</v>
       </c>
       <c r="N13" t="n">
-        <v>48.77</v>
+        <v>13.23</v>
       </c>
       <c r="O13" t="n">
-        <v>954547197000</v>
+        <v>6117170450</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q13" t="n">
-        <v>468000</v>
+        <v>24150</v>
       </c>
       <c r="R13" t="n">
-        <v>-36000</v>
+        <v>11000</v>
       </c>
       <c r="S13" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국내 증시 및 정치 상황에 대한 강한 불만과 함께, 솔리다임 상장 철회 가능성 및 외국인 매도 증가에 대한 우려가 나타남. 전반적으로 부정적인 분위기가 지배적임.</t>
+          <t>HLB의 간암 치료제 FDA 승인 기대감 속 기관 매수세 유입 확인. 다만, 클래스 1/2 판독 불확실성 및 공매도 우려 상존.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '외국인', '솔리다임']</t>
+          <t>['FDA 승인', '간암 치료제', '기관 수급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9930</v>
+        <v>9920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.65%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.53</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H14" t="n">
         <v>5.87</v>
@@ -1714,7 +1714,7 @@
         <v>5.34</v>
       </c>
       <c r="O14" t="n">
-        <v>9527562390</v>
+        <v>9911219160</v>
       </c>
       <c r="P14" t="n">
         <v>14940</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 상장 이슈 등 잠재적 호재와 함께, 공매도 및 개인 물량 털기에 대한 우려가 혼재된 양상. 분봉 차트 분석 및 개미 털기 언급이 나타남.</t>
+          <t>테슬라 실적 호재에도 불구하고 주가 하락 및 대량 매도세에 대한 우려. 공매도 증가 가능성 및 개미 털기 구간으로 해석.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테슬라', '공매도', '차트']</t>
+          <t>['테슬라', '매도세', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10250</v>
+        <v>10260</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.99%</t>
+          <t>'-7.90%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>39956728735</v>
+        <v>41233870460</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 급등 관련 기대감 속 투기 과열 종목 지정 및 ESS 마진율 불확실성 언급. 급락 및 반등 불가 전망.</t>
+          <t>로봇주 강세 속 투자경고 및 예상치 못한 주가 하락에 대한 우려. ESS 마진율 불확실성 등 재료 노출에 따른 하락세 지속 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇주', '투기과열', 'ESS']</t>
+          <t>['로봇주', '투자경고', '하락']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_10.xlsx
+++ b/data/trending_integrated_20261022_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3622</v>
+        <v>3780</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.22%</t>
+          <t>'+22.33%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G2" t="n">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>3190</v>
       </c>
       <c r="L2" t="n">
-        <v>3700</v>
+        <v>3785</v>
       </c>
       <c r="M2" t="n">
         <v>3155</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>35714460534</v>
+        <v>40993208640</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 김정은 위원장 관련 신변 이상설 및 사망설에 따른 급등세. 전쟁 가능성 대두 및 관련주로서의 움직임 집중.</t>
+          <t>북한 김정은 위원장 신변 이상설 및 사망설, 전쟁 가능성 대두에 따른 급등 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은', '신변 이상설', '전쟁']</t>
+          <t>['김정은 신변 이상설', '전쟁 가능성', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55800</v>
+        <v>55700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.98%</t>
+          <t>'+16.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="F3" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G3" t="n">
-        <v>782</v>
+        <v>862</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>411986879450</v>
+        <v>439490734800</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>실적 발표서 역대급 어닝 서프라이즈 기록. 주식 소각 결정 및 전망 상향 공시로 투자 심리 강화. 5천억 영업이익 달성 및 자사주 취득 등으로 주가 상승 기대.</t>
+          <t>호실적 발표 및 주식 소각 결정, 전망 상향, 자사주 취득 공시로 인한 강한 매수세 유입.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7790</v>
+        <v>7740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.97%</t>
+          <t>'+16.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6636540260</v>
+        <v>6730005250</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 기업 루미아 인수 기반 휴머노이드 로봇 사업 관련 호재 집중. 해외 기업 인수 및 기술 개발 성공 시 높은 상승 기대감 표출.</t>
+          <t>미국 기업 루미아 인수 및 휴머노이드 로봇 관련 기술 개발, 긍정적 전망과 점상한가 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['루미아', '인수', '휴머노이드']</t>
+          <t>['루미아 인수', '휴머노이드 로봇', '점상한가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18590</v>
+        <v>18860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.74%</t>
+          <t>'+5.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.32</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H5" t="n">
         <v>3.29</v>
@@ -886,7 +886,7 @@
         <v>3.61</v>
       </c>
       <c r="O5" t="n">
-        <v>58051916050</v>
+        <v>60036307595</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>PHP 해킹 이슈로 인한 보안주 급등 기대감 형성. 하지만 단기 급등 후 개인 매물 출회 및 외국인 단타 흐름 관측.</t>
+          <t>전 세계 보안 이슈 확산 및 PHP 웹사이트 취약점 발견. AI 발전과 연계한 보안 성장주로서의 전망 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안 이슈', 'PHP 해킹', '단기 급등']</t>
+          <t>['보안', 'PHP', 'AI']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1667</v>
+        <v>1694</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.54%</t>
+          <t>'+5.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.39</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -978,7 +978,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8609323682</v>
+        <v>9057255355</v>
       </c>
       <c r="P6" t="n">
         <v>3980</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>매각 관련 불확실성과 주가 급락 경험 후 반등 기대감. 주가 조작 의혹 및 공시 내용에 대한 불만 표출.</t>
+          <t>하한가 두 번에 대한 원인 불명확, 매각 관련 불확실성 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['매각', '주가 조작', '호재']</t>
+          <t>['하한가', '매각 불확실성', '주가 조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14970</v>
+        <v>14720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.35%</t>
+          <t>'-0.34%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1064,13 +1064,13 @@
         <v>15290</v>
       </c>
       <c r="M7" t="n">
-        <v>14770</v>
+        <v>14700</v>
       </c>
       <c r="N7" t="n">
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>25248628630</v>
+        <v>26704879930</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외국인 및 연기금 매수세 유입에 대한 기대감과 실적 우량주로서의 가능성 언급. 정치적 메시지와 주가 조작 의혹 관련 내용 혼재.</t>
+          <t>타 건설주 대비 낮은 상승률 및 경영 방식 비판, 정치적 언급과 함께 대차해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외국인', '연기금', '실적']</t>
+          <t>['건설주', '경영 방식', '대차해지']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15110</v>
+        <v>14170</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.87%</t>
+          <t>'-0.98%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>0.33</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>80</v>
+        <v>318</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>3.48</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14980</v>
+        <v>14310</v>
       </c>
       <c r="K8" t="n">
-        <v>14460</v>
+        <v>14180</v>
       </c>
       <c r="L8" t="n">
-        <v>16140</v>
+        <v>14830</v>
       </c>
       <c r="M8" t="n">
-        <v>13550</v>
+        <v>13890</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>63827544785</v>
+        <v>73451779580</v>
       </c>
       <c r="P8" t="n">
-        <v>28800</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>12030</v>
+        <v>1640</v>
       </c>
       <c r="R8" t="n">
-        <v>-47000</v>
+        <v>-368000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>반도체 섹터 전반의 흐름 및 대만 반도체 파업 관련 소식에 따른 변동성. 신규 상장주 수급 이동 및 AI, 반도체 관련 기대감 언급.</t>
+          <t>엔비디아 AI 광통신 관련 기술 확보 및 기관 매집 시작, 긍정적 전망과 목표 주가 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '수급']</t>
+          <t>['AI 광통신', 'EUV 유리기판', '기관 매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14360</v>
+        <v>14760</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'-1.47%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.33</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="H9" t="n">
-        <v>3.48</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14310</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>14180</v>
+        <v>14460</v>
       </c>
       <c r="L9" t="n">
-        <v>14830</v>
+        <v>16140</v>
       </c>
       <c r="M9" t="n">
-        <v>13890</v>
+        <v>13550</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>70163270950</v>
+        <v>66297733390</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>28800</v>
       </c>
       <c r="Q9" t="n">
-        <v>1640</v>
+        <v>12030</v>
       </c>
       <c r="R9" t="n">
-        <v>-368000</v>
+        <v>-47000</v>
       </c>
       <c r="S9" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>엔비디아 AI 광통신 관련 뉴스 및 EUV용 유리기판 제조 기술 확보 등 구체적인 기술적 호재가 연이어 발생하며 급등 기대감이 고조됨. 기관 매집 시작 및 15000원 돌파 전망이 제시됨.</t>
+          <t>AI 및 반도체 관련 이슈 속 주가 변동성, 수주 잔고 및 시가총액 증가 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '광통신', 'EUV']</t>
+          <t>['AI', '반도체', '수주 잔고']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>220750</v>
+        <v>7200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.23%</t>
+          <t>'-2.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>460</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>1862</v>
+        <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>46.14</v>
+        <v>25.47</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>223500</v>
+        <v>7350</v>
       </c>
       <c r="K10" t="n">
-        <v>221500</v>
+        <v>7270</v>
       </c>
       <c r="L10" t="n">
-        <v>226000</v>
+        <v>7340</v>
       </c>
       <c r="M10" t="n">
-        <v>219500</v>
+        <v>7190</v>
       </c>
       <c r="N10" t="n">
-        <v>46.08</v>
+        <v>25.45</v>
       </c>
       <c r="O10" t="n">
-        <v>803980517500</v>
+        <v>6328686060</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>7190</v>
       </c>
       <c r="R10" t="n">
-        <v>-89000</v>
+        <v>-47000</v>
       </c>
       <c r="S10" t="n">
-        <v>-156000</v>
+        <v>-18000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외국인 거래 패턴에 대한 불만과 함께 반도체 섹터 전반의 흐름에 따른 하락세 지속 전망. 일부 긍정적 전망도 있으나 객관적 근거 부족.</t>
+          <t>지속적인 적자와 낮은 주가 수준에 대한 불만. 실적 부진에도 불구하고 바닥권이라는 인식과 함께 단기 반등 가능성 언급. OLED 관련 뉴스 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외국인', '반도체', '수급']</t>
+          <t>['실적 부진', '바닥권', 'OLED']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7240</v>
+        <v>41250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-2.60%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>236</v>
+        <v>605</v>
       </c>
       <c r="H11" t="n">
-        <v>25.47</v>
+        <v>13.09</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7350</v>
+        <v>42350</v>
       </c>
       <c r="K11" t="n">
-        <v>7270</v>
+        <v>41850</v>
       </c>
       <c r="L11" t="n">
-        <v>7340</v>
+        <v>42350</v>
       </c>
       <c r="M11" t="n">
-        <v>7210</v>
+        <v>41150</v>
       </c>
       <c r="N11" t="n">
-        <v>25.45</v>
+        <v>13.23</v>
       </c>
       <c r="O11" t="n">
-        <v>5249091955</v>
+        <v>6595154425</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>7190</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-47000</v>
+        <v>11000</v>
       </c>
       <c r="S11" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>지속적인 적자와 낮은 주가 수준에 대한 불만. 실적 부진에도 불구하고 바닥권이라는 인식과 함께 단기 반등 가능성 언급. OLED 관련 뉴스 혼재.</t>
+          <t>HLB, 기관 매수세 유입 속 주가 하락. 간암 치료제 C1/C2 승인에 대한 기대감 및 불확실성 공존.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적 부진', '바닥권', 'OLED']</t>
+          <t>['간암', 'FDA 승인', '기관']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1272000</v>
+        <v>217250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-2.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>503</v>
+        <v>454</v>
       </c>
       <c r="G12" t="n">
-        <v>1789</v>
+        <v>1669</v>
       </c>
       <c r="H12" t="n">
-        <v>48.79</v>
+        <v>46.14</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1294000</v>
+        <v>223500</v>
       </c>
       <c r="K12" t="n">
-        <v>1273000</v>
+        <v>221500</v>
       </c>
       <c r="L12" t="n">
-        <v>1297000</v>
+        <v>226000</v>
       </c>
       <c r="M12" t="n">
-        <v>1266000</v>
+        <v>217000</v>
       </c>
       <c r="N12" t="n">
-        <v>48.77</v>
+        <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>990274500500</v>
+        <v>913777807500</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>468000</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>-36000</v>
+        <v>-89000</v>
       </c>
       <c r="S12" t="n">
-        <v>10000</v>
+        <v>-156000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 리스크 및 경영진 관련 부정적 언급과 함께 외국인 매도세 증가, 주가 하락에 대한 불만 표출. 일부 긍정적 수급 변화 가능성 언급.</t>
+          <t>국내 증시 하락 및 정치적 불확실성 언급, 삼성전자 주가 부진에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치적 리스크', '외국인', '주가 하락']</t>
+          <t>['국내 증시', '정치적 불확실성', '주가 부진']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41500</v>
+        <v>1251000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-3.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>128</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>502</v>
       </c>
       <c r="G13" t="n">
-        <v>550</v>
+        <v>1677</v>
       </c>
       <c r="H13" t="n">
-        <v>13.09</v>
+        <v>48.79</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>42350</v>
+        <v>1294000</v>
       </c>
       <c r="K13" t="n">
-        <v>41850</v>
+        <v>1273000</v>
       </c>
       <c r="L13" t="n">
-        <v>42350</v>
+        <v>1297000</v>
       </c>
       <c r="M13" t="n">
-        <v>41150</v>
+        <v>1248000</v>
       </c>
       <c r="N13" t="n">
-        <v>13.23</v>
+        <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>6117170450</v>
+        <v>1108129668500</v>
       </c>
       <c r="P13" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>24150</v>
+        <v>468000</v>
       </c>
       <c r="R13" t="n">
-        <v>11000</v>
+        <v>-36000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>HLB의 간암 치료제 FDA 승인 기대감 속 기관 매수세 유입 확인. 다만, 클래스 1/2 판독 불확실성 및 공매도 우려 상존.</t>
+          <t>정치적 요인 및 경영진 관련 불만, 외국인 매도 증가와 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 치료제', '기관 수급']</t>
+          <t>['정치적 요인', '경영진', '외국인 매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9920</v>
+        <v>9830</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.65%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.53</v>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F14" t="n">
         <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H14" t="n">
         <v>5.87</v>
@@ -1714,7 +1714,7 @@
         <v>5.34</v>
       </c>
       <c r="O14" t="n">
-        <v>9911219160</v>
+        <v>10311919945</v>
       </c>
       <c r="P14" t="n">
         <v>14940</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>테슬라 실적 호재에도 불구하고 주가 하락 및 대량 매도세에 대한 우려. 공매도 증가 가능성 및 개미 털기 구간으로 해석.</t>
+          <t>테슬라 실적 상회 및 스페이스X 상장 이슈, 공매도와 개미 털기 구간에 대한 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테슬라', '매도세', '공매도']</t>
+          <t>['테슬라', '스페이스X', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10260</v>
+        <v>10130</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.90%</t>
+          <t>'-9.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F15" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G15" t="n">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>41233870460</v>
+        <v>42443886095</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 강세 속 투자경고 및 예상치 못한 주가 하락에 대한 우려. ESS 마진율 불확실성 등 재료 노출에 따른 하락세 지속 가능성 언급.</t>
+          <t>로봇주 급등 후 투자경고 종목 지정 및 급락. ESS 마진율 불확실성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇주', '투자경고', '하락']</t>
+          <t>['투자경고', '급락', 'ESS']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261022_10.xlsx
+++ b/data/trending_integrated_20261022_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3780</v>
+        <v>3785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.33%</t>
+          <t>'+22.49%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="F2" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>324</v>
+        <v>369</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>3190</v>
       </c>
       <c r="L2" t="n">
-        <v>3785</v>
+        <v>3870</v>
       </c>
       <c r="M2" t="n">
         <v>3155</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>40993208640</v>
+        <v>48391487199</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 김정은 위원장 신변 이상설 및 사망설, 전쟁 가능성 대두에 따른 급등 기대.</t>
+          <t>김정은 신변 이상설 및 사망설에 따른 전쟁 가능성 대두. 급등 및 VI 발동.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은 신변 이상설', '전쟁 가능성', '급등']</t>
+          <t>['김정은', '신변 이상설', '전쟁 가능성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>유니켐</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55700</v>
+        <v>7770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.77%</t>
+          <t>'+16.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>213</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>862</v>
+        <v>84</v>
       </c>
       <c r="H3" t="n">
-        <v>37.72</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>47700</v>
+        <v>6660</v>
       </c>
       <c r="K3" t="n">
-        <v>51000</v>
+        <v>6710</v>
       </c>
       <c r="L3" t="n">
-        <v>56500</v>
+        <v>8430</v>
       </c>
       <c r="M3" t="n">
-        <v>50500</v>
+        <v>6640</v>
       </c>
       <c r="N3" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>439490734800</v>
+        <v>6835817800</v>
       </c>
       <c r="P3" t="n">
-        <v>67300</v>
+        <v>8430</v>
       </c>
       <c r="Q3" t="n">
-        <v>23150</v>
+        <v>391</v>
       </c>
       <c r="R3" t="n">
-        <v>1440000</v>
+        <v>14000</v>
       </c>
       <c r="S3" t="n">
-        <v>368000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>호실적 발표 및 주식 소각 결정, 전망 상향, 자사주 취득 공시로 인한 강한 매수세 유입.</t>
+          <t>미국 기업 루미아 인수 관련 기대감 상승. 휴머노이드 로봇 사업 확장 전망 및 50배 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '주식 소각', '전망 상향']</t>
+          <t>['루미아 인수', '휴머노이드 로봇', '사업 확장']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>011330</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>유니켐</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7740</v>
+        <v>55600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.22%</t>
+          <t>'+16.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>225</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="G4" t="n">
-        <v>79</v>
+        <v>905</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>37.72</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6660</v>
+        <v>47700</v>
       </c>
       <c r="K4" t="n">
-        <v>6710</v>
+        <v>51000</v>
       </c>
       <c r="L4" t="n">
-        <v>8430</v>
+        <v>56500</v>
       </c>
       <c r="M4" t="n">
-        <v>6640</v>
+        <v>50500</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="O4" t="n">
-        <v>6730005250</v>
+        <v>448749913600</v>
       </c>
       <c r="P4" t="n">
-        <v>8430</v>
+        <v>67300</v>
       </c>
       <c r="Q4" t="n">
-        <v>391</v>
+        <v>23150</v>
       </c>
       <c r="R4" t="n">
-        <v>14000</v>
+        <v>1440000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>368000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 기업 루미아 인수 및 휴머노이드 로봇 관련 기술 개발, 긍정적 전망과 점상한가 기대.</t>
+          <t>실적 발표 어닝 서프라이즈 및 주식 소각 결정, 전망 상향 공시. 자사주 취득 동시 진행.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['루미아 인수', '휴머노이드 로봇', '점상한가']</t>
+          <t>['어닝 서프라이즈', '실적 발표', '주식 소각']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>011330</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18860</v>
+        <v>18830</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.25%</t>
+          <t>'+5.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.32</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
         <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H5" t="n">
         <v>3.29</v>
@@ -886,7 +886,7 @@
         <v>3.61</v>
       </c>
       <c r="O5" t="n">
-        <v>60036307595</v>
+        <v>61330081020</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>전 세계 보안 이슈 확산 및 PHP 웹사이트 취약점 발견. AI 발전과 연계한 보안 성장주로서의 전망 제시.</t>
+          <t>미국 보안주 초급등 및 보안 이슈 확산에 따른 라온시큐어 주목. AI 발전과 함께 보안 산업 성장 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안', 'PHP', 'AI']</t>
+          <t>['보안', 'AI', 'PHP']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1694</v>
+        <v>1672</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.22%</t>
+          <t>'+3.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.39</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -978,7 +978,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>9057255355</v>
+        <v>9273586320</v>
       </c>
       <c r="P6" t="n">
         <v>3980</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>하한가 두 번에 대한 원인 불명확, 매각 관련 불확실성 속 투자자 혼란.</t>
+          <t>매각 관련 불확실성 속 주가조작 및 하한가에 대한 언급. 향후 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['하한가', '매각 불확실성', '주가 조작']</t>
+          <t>['매각', '주가조작', '공시']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14720</v>
+        <v>14470</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.34%</t>
+          <t>'+1.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>162</v>
+        <v>324</v>
       </c>
       <c r="H7" t="n">
-        <v>9.949999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14770</v>
+        <v>14310</v>
       </c>
       <c r="K7" t="n">
-        <v>14770</v>
+        <v>14180</v>
       </c>
       <c r="L7" t="n">
-        <v>15290</v>
+        <v>14830</v>
       </c>
       <c r="M7" t="n">
-        <v>14700</v>
+        <v>13890</v>
       </c>
       <c r="N7" t="n">
-        <v>9.82</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>26704879930</v>
+        <v>75665757965</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R7" t="n">
-        <v>-95000</v>
+        <v>-368000</v>
       </c>
       <c r="S7" t="n">
-        <v>-14000</v>
+        <v>9000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>타 건설주 대비 낮은 상승률 및 경영 방식 비판, 정치적 언급과 함께 대차해지 운동 촉구.</t>
+          <t>엔비디아 AI 광통신 관련 기술 확보 및 기관 매집 시작, 긍정적 전망과 목표 주가 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['건설주', '경영 방식', '대차해지']</t>
+          <t>['AI 광통신', 'EUV 유리기판', '기관 매집']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14170</v>
+        <v>14830</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.98%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>318</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>3.48</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14310</v>
+        <v>14770</v>
       </c>
       <c r="K8" t="n">
-        <v>14180</v>
+        <v>14770</v>
       </c>
       <c r="L8" t="n">
-        <v>14830</v>
+        <v>15290</v>
       </c>
       <c r="M8" t="n">
-        <v>13890</v>
+        <v>14700</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>9.82</v>
       </c>
       <c r="O8" t="n">
-        <v>73451779580</v>
+        <v>27551594480</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>1640</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-368000</v>
+        <v>-95000</v>
       </c>
       <c r="S8" t="n">
-        <v>9000</v>
+        <v>-14000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>엔비디아 AI 광통신 관련 기술 확보 및 기관 매집 시작, 긍정적 전망과 목표 주가 언급.</t>
+          <t>타 건설주 대비 낮은 상승률 및 경영 방식 비판, 정치적 언급과 함께 대차해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI 광통신', 'EUV 유리기판', '기관 매집']</t>
+          <t>['건설주', '경영 방식', '대차해지']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14760</v>
+        <v>7220</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.47%</t>
+          <t>'-1.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2</v>
+        <v>25.47</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>7350</v>
       </c>
       <c r="K9" t="n">
-        <v>14460</v>
+        <v>7270</v>
       </c>
       <c r="L9" t="n">
-        <v>16140</v>
+        <v>7340</v>
       </c>
       <c r="M9" t="n">
-        <v>13550</v>
+        <v>7190</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>25.45</v>
       </c>
       <c r="O9" t="n">
-        <v>66297733390</v>
+        <v>6622696045</v>
       </c>
       <c r="P9" t="n">
-        <v>28800</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>12030</v>
+        <v>7190</v>
       </c>
       <c r="R9" t="n">
         <v>-47000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 및 반도체 관련 이슈 속 주가 변동성, 수주 잔고 및 시가총액 증가 기대.</t>
+          <t>지속적인 적자와 낮은 주가 수준에 대한 불만. 실적 부진에도 불구하고 바닥권이라는 인식과 함께 단기 반등 가능성 언급. OLED 관련 뉴스 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '수주 잔고']</t>
+          <t>['실적 부진', '바닥권', 'OLED']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7200</v>
+        <v>41550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.04%</t>
+          <t>'-1.89%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="G10" t="n">
-        <v>246</v>
+        <v>612</v>
       </c>
       <c r="H10" t="n">
-        <v>25.47</v>
+        <v>13.09</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7350</v>
+        <v>42350</v>
       </c>
       <c r="K10" t="n">
-        <v>7270</v>
+        <v>41850</v>
       </c>
       <c r="L10" t="n">
-        <v>7340</v>
+        <v>42350</v>
       </c>
       <c r="M10" t="n">
-        <v>7190</v>
+        <v>41150</v>
       </c>
       <c r="N10" t="n">
-        <v>25.45</v>
+        <v>13.23</v>
       </c>
       <c r="O10" t="n">
-        <v>6328686060</v>
+        <v>6798146525</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>7190</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-47000</v>
+        <v>11000</v>
       </c>
       <c r="S10" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>지속적인 적자와 낮은 주가 수준에 대한 불만. 실적 부진에도 불구하고 바닥권이라는 인식과 함께 단기 반등 가능성 언급. OLED 관련 뉴스 혼재.</t>
+          <t>간암 치료제 FDA 승인에 대한 기대감 속에서 기관 매수세가 확인되었으나, 투자자들의 혼조된 심리와 불확실성이 공존함. C2 임상 결과에 따른 변동성 가능성이 제기됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적 부진', '바닥권', 'OLED']</t>
+          <t>['FDA 승인', '간암 치료제', '기관 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41250</v>
+        <v>9940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.60%</t>
+          <t>'-2.45%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.14</v>
+        <v>0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>605</v>
+        <v>278</v>
       </c>
       <c r="H11" t="n">
-        <v>13.09</v>
+        <v>5.87</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>42350</v>
+        <v>10190</v>
       </c>
       <c r="K11" t="n">
-        <v>41850</v>
+        <v>10110</v>
       </c>
       <c r="L11" t="n">
-        <v>42350</v>
+        <v>10180</v>
       </c>
       <c r="M11" t="n">
-        <v>41150</v>
+        <v>9720</v>
       </c>
       <c r="N11" t="n">
-        <v>13.23</v>
+        <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>6595154425</v>
+        <v>11322016690</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>14940</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>5390</v>
       </c>
       <c r="R11" t="n">
-        <v>11000</v>
+        <v>-84000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>HLB, 기관 매수세 유입 속 주가 하락. 간암 치료제 C1/C2 승인에 대한 기대감 및 불확실성 공존.</t>
+          <t>테슬라 실적 상회 및 스페이스X 이슈 관련 기대와 매물 출회 혼재. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['간암', 'FDA 승인', '기관']</t>
+          <t>['테슬라', '실적', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>217250</v>
+        <v>14600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.80%</t>
+          <t>'-2.54%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F12" t="n">
-        <v>454</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>1669</v>
+        <v>85</v>
       </c>
       <c r="H12" t="n">
-        <v>46.14</v>
+        <v>1.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>223500</v>
+        <v>14980</v>
       </c>
       <c r="K12" t="n">
-        <v>221500</v>
+        <v>14460</v>
       </c>
       <c r="L12" t="n">
-        <v>226000</v>
+        <v>16140</v>
       </c>
       <c r="M12" t="n">
-        <v>217000</v>
+        <v>13550</v>
       </c>
       <c r="N12" t="n">
-        <v>46.08</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>913777807500</v>
+        <v>66964780750</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>28800</v>
       </c>
       <c r="Q12" t="n">
-        <v>94500</v>
+        <v>12030</v>
       </c>
       <c r="R12" t="n">
-        <v>-89000</v>
+        <v>-47000</v>
       </c>
       <c r="S12" t="n">
-        <v>-156000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 증시 하락 및 정치적 불확실성 언급, 삼성전자 주가 부진에 대한 불만 표출.</t>
+          <t>AI, 반도체 관련 뉴스 및 신규 상장주 영향 속 주가 등락. 수주잔고 및 시총 관련 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국내 증시', '정치적 불확실성', '주가 부진']</t>
+          <t>['AI', '반도체', '수주잔고']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1251000</v>
+        <v>217500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.32%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>502</v>
+        <v>454</v>
       </c>
       <c r="G13" t="n">
-        <v>1677</v>
+        <v>1548</v>
       </c>
       <c r="H13" t="n">
-        <v>48.79</v>
+        <v>46.14</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1294000</v>
+        <v>223500</v>
       </c>
       <c r="K13" t="n">
-        <v>1273000</v>
+        <v>221500</v>
       </c>
       <c r="L13" t="n">
-        <v>1297000</v>
+        <v>226000</v>
       </c>
       <c r="M13" t="n">
-        <v>1248000</v>
+        <v>217000</v>
       </c>
       <c r="N13" t="n">
-        <v>48.77</v>
+        <v>46.08</v>
       </c>
       <c r="O13" t="n">
-        <v>1108129668500</v>
+        <v>950054147250</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>468000</v>
+        <v>94500</v>
       </c>
       <c r="R13" t="n">
-        <v>-36000</v>
+        <v>-89000</v>
       </c>
       <c r="S13" t="n">
-        <v>10000</v>
+        <v>-156000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 요인 및 경영진 관련 불만, 외국인 매도 증가와 주가 하락에 대한 우려.</t>
+          <t>정치적 이슈와 외국인 수급 불균형에 대한 부정적 전망. 시장 전반에 대한 불신 심화.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치적 요인', '경영진', '외국인 매도']</t>
+          <t>['정치', '외국인 수급', '시장 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9830</v>
+        <v>1254000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-3.09%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>58</v>
+        <v>506</v>
       </c>
       <c r="G14" t="n">
-        <v>264</v>
+        <v>1642</v>
       </c>
       <c r="H14" t="n">
-        <v>5.87</v>
+        <v>48.79</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10190</v>
+        <v>1294000</v>
       </c>
       <c r="K14" t="n">
-        <v>10110</v>
+        <v>1273000</v>
       </c>
       <c r="L14" t="n">
-        <v>10180</v>
+        <v>1297000</v>
       </c>
       <c r="M14" t="n">
-        <v>9720</v>
+        <v>1248000</v>
       </c>
       <c r="N14" t="n">
-        <v>5.34</v>
+        <v>48.77</v>
       </c>
       <c r="O14" t="n">
-        <v>10311919945</v>
+        <v>1148674112500</v>
       </c>
       <c r="P14" t="n">
-        <v>14940</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>5390</v>
+        <v>468000</v>
       </c>
       <c r="R14" t="n">
-        <v>-84000</v>
+        <v>-36000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 상장 이슈, 공매도와 개미 털기 구간에 대한 언급.</t>
+          <t>최태원 관련 이슈 및 정치적 언급과 함께 외국인 매도 증가에 대한 부정적 전망. 솔리다임 상장 철회 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '공매도']</t>
+          <t>['최태원', '외국인 매도', '정치']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10130</v>
+        <v>10220</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.07%</t>
+          <t>'-8.26%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.41</v>
       </c>
       <c r="E15" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G15" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="H15" t="n">
         <v>3.69</v>
@@ -1806,7 +1806,7 @@
         <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>42443886095</v>
+        <v>43154752620</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇주 급등 후 투자경고 종목 지정 및 급락. ESS 마진율 불확실성 언급.</t>
+          <t>로봇주 NXT 시장 폭등 및 투자경고, 투기예고 관련 이슈. ESS 마진율 불확실성 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['투자경고', '급락', 'ESS']</t>
+          <t>['로봇주', '투자경고', 'ESS']</t>
         </is>
       </c>
       <c r="X15" t="n">
